--- a/Data/National Accounts/PSA-13TRD_2018PSNA_Ann.xlsx
+++ b/Data/National Accounts/PSA-13TRD_2018PSNA_Ann.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Annl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Annl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37864FF7-7E4E-4F70-8F36-2596CBE8DDE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD73C0F-4050-421F-ACA1-B502DA157591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TRD" sheetId="1" r:id="rId1"/>
@@ -613,9 +613,6 @@
     <t>2023 - 2024</t>
   </si>
   <si>
-    <t>As of January 2026</t>
-  </si>
-  <si>
     <t>Annual 2000 to 2025</t>
   </si>
   <si>
@@ -623,6 +620,9 @@
   </si>
   <si>
     <t>2024 - 2025</t>
+  </si>
+  <si>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -23598,7 +23598,7 @@
     </row>
     <row r="3" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:96" x14ac:dyDescent="0.2">
@@ -23608,7 +23608,7 @@
     </row>
     <row r="6" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:96" x14ac:dyDescent="0.2">
@@ -23810,10 +23810,10 @@
         <v>740182.79701482842</v>
       </c>
       <c r="Z12" s="8">
-        <v>787021.76034125127</v>
+        <v>785004.57932968577</v>
       </c>
       <c r="AA12" s="8">
-        <v>829916.41863247391</v>
+        <v>827926.19185333338</v>
       </c>
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
@@ -23962,10 +23962,10 @@
         <v>3602949.7526950426</v>
       </c>
       <c r="Z13" s="8">
-        <v>3978662.1688061003</v>
+        <v>3978959.3988652546</v>
       </c>
       <c r="AA13" s="8">
-        <v>4247293.5455214409</v>
+        <v>4250672.5784621667</v>
       </c>
       <c r="AB13" s="9"/>
       <c r="AC13" s="9"/>
@@ -24114,10 +24114,10 @@
         <v>102250.44848216053</v>
       </c>
       <c r="Z14" s="8">
-        <v>111071.96102639954</v>
+        <v>111159.95245571183</v>
       </c>
       <c r="AA14" s="8">
-        <v>120346.98697336629</v>
+        <v>119237.97931223176</v>
       </c>
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
@@ -24364,10 +24364,10 @@
         <v>4445382.9981920319</v>
       </c>
       <c r="Z16" s="11">
-        <v>4876755.8901737509</v>
+        <v>4875123.9306506524</v>
       </c>
       <c r="AA16" s="11">
-        <v>5197556.9511272814</v>
+        <v>5197836.7496277317</v>
       </c>
       <c r="AB16" s="9"/>
       <c r="AC16" s="9"/>
@@ -24681,7 +24681,7 @@
     </row>
     <row r="23" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:96" x14ac:dyDescent="0.2">
@@ -24691,7 +24691,7 @@
     </row>
     <row r="26" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:96" x14ac:dyDescent="0.2">
@@ -24893,10 +24893,10 @@
         <v>622276.2729538749</v>
       </c>
       <c r="Z32" s="8">
-        <v>644964.28108495846</v>
+        <v>643351.00175087457</v>
       </c>
       <c r="AA32" s="8">
-        <v>659701.22076511767</v>
+        <v>658229.00054999324</v>
       </c>
       <c r="AB32" s="9"/>
       <c r="AC32" s="9"/>
@@ -25045,10 +25045,10 @@
         <v>3193102.3671750077</v>
       </c>
       <c r="Z33" s="8">
-        <v>3383056.8919933802</v>
+        <v>3383307.4048906201</v>
       </c>
       <c r="AA33" s="8">
-        <v>3576682.2409391636</v>
+        <v>3579538.0725344904</v>
       </c>
       <c r="AB33" s="9"/>
       <c r="AC33" s="9"/>
@@ -25197,10 +25197,10 @@
         <v>99221.026132761981</v>
       </c>
       <c r="Z34" s="8">
-        <v>106449.04401460002</v>
+        <v>106533.54548463774</v>
       </c>
       <c r="AA34" s="8">
-        <v>113920.75661309918</v>
+        <v>112876.43538359046</v>
       </c>
       <c r="AB34" s="9"/>
       <c r="AC34" s="9"/>
@@ -25447,10 +25447,10 @@
         <v>3914599.6662616446</v>
       </c>
       <c r="Z36" s="11">
-        <v>4134470.2170929387</v>
+        <v>4133191.9521261323</v>
       </c>
       <c r="AA36" s="11">
-        <v>4350304.2183173802</v>
+        <v>4350643.5084680747</v>
       </c>
       <c r="AB36" s="9"/>
       <c r="AC36" s="9"/>
@@ -25764,7 +25764,7 @@
     </row>
     <row r="43" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45" spans="1:96" x14ac:dyDescent="0.2">
@@ -25774,7 +25774,7 @@
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47" spans="1:96" x14ac:dyDescent="0.2">
@@ -25890,7 +25890,7 @@
         <v>47</v>
       </c>
       <c r="Z50" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AA50" s="16"/>
     </row>
@@ -25971,10 +25971,10 @@
         <v>6.8749817213010971</v>
       </c>
       <c r="Y52" s="17">
-        <v>6.3280264706671403</v>
+        <v>6.0555017619464451</v>
       </c>
       <c r="Z52" s="17">
-        <v>5.4502506096684868</v>
+        <v>5.4676894446015041</v>
       </c>
       <c r="AA52" s="17"/>
       <c r="AB52" s="9"/>
@@ -26116,10 +26116,10 @@
         <v>12.335886454298389</v>
       </c>
       <c r="Y53" s="17">
-        <v>10.427911625190475</v>
+        <v>10.436161256174969</v>
       </c>
       <c r="Z53" s="17">
-        <v>6.7518016186820518</v>
+        <v>6.8287497398038539</v>
       </c>
       <c r="AA53" s="17"/>
       <c r="AB53" s="9"/>
@@ -26261,10 +26261,10 @@
         <v>16.617599074802854</v>
       </c>
       <c r="Y54" s="17">
-        <v>8.6273582905390214</v>
+        <v>8.7134131006826152</v>
       </c>
       <c r="Z54" s="17">
-        <v>8.3504656452065831</v>
+        <v>7.2670297873133478</v>
       </c>
       <c r="AA54" s="17"/>
       <c r="AB54" s="9"/>
@@ -26499,10 +26499,10 @@
         <v>11.481569513907132</v>
       </c>
       <c r="Y56" s="17">
-        <v>9.7038408649414691</v>
+        <v>9.667129528173362</v>
       </c>
       <c r="Z56" s="17">
-        <v>6.578165243003383</v>
+        <v>6.6195818520250214</v>
       </c>
       <c r="AA56" s="17"/>
       <c r="AB56" s="9"/>
@@ -26802,7 +26802,7 @@
     </row>
     <row r="63" spans="1:91" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65" spans="1:92" x14ac:dyDescent="0.2">
@@ -26812,7 +26812,7 @@
     </row>
     <row r="66" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="67" spans="1:92" x14ac:dyDescent="0.2">
@@ -26928,7 +26928,7 @@
         <v>47</v>
       </c>
       <c r="Z70" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AA70" s="6"/>
     </row>
@@ -27009,10 +27009,10 @@
         <v>1.7770535411938368</v>
       </c>
       <c r="Y72" s="17">
-        <v>3.6459703056628001</v>
+        <v>3.3867157905539784</v>
       </c>
       <c r="Z72" s="17">
-        <v>2.2849233844963948</v>
+        <v>2.3125787880376834</v>
       </c>
       <c r="AA72" s="17"/>
       <c r="AB72" s="9"/>
@@ -27154,10 +27154,10 @@
         <v>6.0114699891611991</v>
       </c>
       <c r="Y73" s="17">
-        <v>5.948901819468702</v>
+        <v>5.9567472584316334</v>
       </c>
       <c r="Z73" s="17">
-        <v>5.7233843570302554</v>
+        <v>5.7999656596446414</v>
       </c>
       <c r="AA73" s="17"/>
       <c r="AB73" s="9"/>
@@ -27299,10 +27299,10 @@
         <v>13.605054884947137</v>
       </c>
       <c r="Y74" s="17">
-        <v>7.2847642919623183</v>
+        <v>7.3699291741765336</v>
       </c>
       <c r="Z74" s="17">
-        <v>7.019050915548263</v>
+        <v>5.9538898007176329</v>
       </c>
       <c r="AA74" s="17"/>
       <c r="AB74" s="9"/>
@@ -27537,10 +27537,10 @@
         <v>5.4925078463794534</v>
       </c>
       <c r="Y76" s="17">
-        <v>5.6166803652048856</v>
+        <v>5.5840265799960775</v>
       </c>
       <c r="Z76" s="17">
-        <v>5.2203544805360877</v>
+        <v>5.2611047069828061</v>
       </c>
       <c r="AA76" s="17"/>
       <c r="AB76" s="9"/>
@@ -27836,7 +27836,7 @@
     </row>
     <row r="82" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="84" spans="1:96" x14ac:dyDescent="0.2">
@@ -27846,7 +27846,7 @@
     </row>
     <row r="85" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="86" spans="1:96" x14ac:dyDescent="0.2">
@@ -28048,10 +28048,10 @@
         <v>118.94761686819018</v>
       </c>
       <c r="Z91" s="17">
-        <v>122.02563512778161</v>
+        <v>122.01808611369253</v>
       </c>
       <c r="AA91" s="17">
-        <v>125.80186188983274</v>
+        <v>125.78087430993577</v>
       </c>
       <c r="AB91" s="9"/>
       <c r="AC91" s="9"/>
@@ -28200,10 +28200,10 @@
         <v>112.83539762875294</v>
       </c>
       <c r="Z92" s="17">
-        <v>117.60553534356247</v>
+        <v>117.60561257642775</v>
       </c>
       <c r="AA92" s="17">
-        <v>118.74953544674376</v>
+        <v>118.74919311732532</v>
       </c>
       <c r="AB92" s="9"/>
       <c r="AC92" s="9"/>
@@ -28352,10 +28352,10 @@
         <v>103.0532060264576</v>
       </c>
       <c r="Z93" s="17">
-        <v>104.34284502467253</v>
+        <v>104.34267624345725</v>
       </c>
       <c r="AA93" s="17">
-        <v>105.64096530897531</v>
+        <v>105.63584764793707</v>
       </c>
       <c r="AB93" s="9"/>
       <c r="AC93" s="9"/>
@@ -28602,10 +28602,10 @@
         <v>113.55907058657861</v>
       </c>
       <c r="Z95" s="17">
-        <v>117.95358616956572</v>
+        <v>117.95058122434567</v>
       </c>
       <c r="AA95" s="17">
-        <v>119.47571227875193</v>
+        <v>119.47282602012055</v>
       </c>
       <c r="AB95" s="9"/>
       <c r="AC95" s="9"/>
@@ -28723,7 +28723,7 @@
     </row>
     <row r="102" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="104" spans="1:96" x14ac:dyDescent="0.2">
@@ -28733,7 +28733,7 @@
     </row>
     <row r="105" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="106" spans="1:96" x14ac:dyDescent="0.2">
@@ -28935,10 +28935,10 @@
         <v>16.650596749838336</v>
       </c>
       <c r="Z111" s="17">
-        <v>16.138223402303844</v>
+        <v>16.102248691448466</v>
       </c>
       <c r="AA111" s="17">
-        <v>15.967432900422111</v>
+        <v>15.928283856022013</v>
       </c>
       <c r="AB111" s="9"/>
       <c r="AC111" s="9"/>
@@ -29087,10 +29087,10 @@
         <v>81.04925389241798</v>
       </c>
       <c r="Z112" s="17">
-        <v>81.584197741428213</v>
+        <v>81.617605120742184</v>
       </c>
       <c r="AA112" s="17">
-        <v>81.717114126094543</v>
+        <v>81.777723757226482</v>
       </c>
       <c r="AB112" s="9"/>
       <c r="AC112" s="9"/>
@@ -29239,10 +29239,10 @@
         <v>2.3001493577436745</v>
       </c>
       <c r="Z113" s="17">
-        <v>2.2775788562679571</v>
+        <v>2.2801461878093425</v>
       </c>
       <c r="AA113" s="17">
-        <v>2.3154529734833331</v>
+        <v>2.2939923867514995</v>
       </c>
       <c r="AB113" s="9"/>
       <c r="AC113" s="9"/>
@@ -29806,7 +29806,7 @@
     </row>
     <row r="122" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="124" spans="1:96" x14ac:dyDescent="0.2">
@@ -29816,7 +29816,7 @@
     </row>
     <row r="125" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="126" spans="1:96" x14ac:dyDescent="0.2">
@@ -30018,10 +30018,10 @@
         <v>15.896294027637694</v>
       </c>
       <c r="Z131" s="17">
-        <v>15.599683809996117</v>
+        <v>15.565476009889451</v>
       </c>
       <c r="AA131" s="17">
-        <v>15.164484772981654</v>
+        <v>15.129463015501477</v>
       </c>
       <c r="AB131" s="9"/>
       <c r="AC131" s="9"/>
@@ -30170,10 +30170,10 @@
         <v>81.569065534212072</v>
       </c>
       <c r="Z132" s="17">
-        <v>81.825644262884595</v>
+        <v>81.857011338421671</v>
       </c>
       <c r="AA132" s="17">
-        <v>82.216830397267259</v>
+        <v>82.276060209651561</v>
       </c>
       <c r="AB132" s="9"/>
       <c r="AC132" s="9"/>
@@ -30322,10 +30322,10 @@
         <v>2.5346404381502396</v>
       </c>
       <c r="Z133" s="17">
-        <v>2.5746719271192937</v>
+        <v>2.577512651688882</v>
       </c>
       <c r="AA133" s="17">
-        <v>2.6186848297510945</v>
+        <v>2.5944767748469446</v>
       </c>
       <c r="AB133" s="9"/>
       <c r="AC133" s="9"/>
